--- a/SS_floodwall_input.xlsx
+++ b/SS_floodwall_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD982B7-8048-4CB7-B202-370B02859C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57B7B76-8534-427A-8CAB-710F8AB36996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="23955" windowHeight="20985" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
+    <workbookView xWindow="6285" yWindow="2535" windowWidth="28800" windowHeight="15255" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
   </bookViews>
   <sheets>
     <sheet name="FloodWall" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="140">
   <si>
     <t>NA</t>
   </si>
@@ -59,12 +59,6 @@
     <t>compute_p1</t>
   </si>
   <si>
-    <t>Bottom Slope To Use For Damaging Dpeths (tanb)</t>
-  </si>
-  <si>
-    <t>compute_damaging_depth_slope</t>
-  </si>
-  <si>
     <t>Shielding Parameter To Use For Damaging Depths</t>
   </si>
   <si>
@@ -432,6 +426,36 @@
   </si>
   <si>
     <t>..\CHS_Dependencies</t>
+  </si>
+  <si>
+    <t>Add Toe Berm To Vertical Wall</t>
+  </si>
+  <si>
+    <t>berm_crest_elevation</t>
+  </si>
+  <si>
+    <t>berm_seaward_slope</t>
+  </si>
+  <si>
+    <t>Berm Crest Elevation</t>
+  </si>
+  <si>
+    <t>Berm Seaward Slope (cota)</t>
+  </si>
+  <si>
+    <t>offshore_slope</t>
+  </si>
+  <si>
+    <t>Offshore slope (cota)</t>
+  </si>
+  <si>
+    <t>add_toe_berm</t>
+  </si>
+  <si>
+    <t>berm_crest_width</t>
+  </si>
+  <si>
+    <t>Berm Crest Width</t>
   </si>
 </sst>
 </file>
@@ -480,7 +504,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,12 +514,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00FFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -705,34 +723,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -744,14 +757,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -776,43 +789,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -824,11 +827,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1144,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDE711C-012D-4C9C-BCEB-7FA13A47BF68}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.7109375" customWidth="1"/>
@@ -1158,911 +1162,967 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="F1" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="35">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="4">
+        <v>176.45</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="15">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="16">
+        <v>180.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="16">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="16">
+        <v>175.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="16">
+        <f>1/8</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="16">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="F1" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="44">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="C51" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I10" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="10">
-        <v>176.45</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="10">
+      <c r="B57" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
+      <c r="C57" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="10">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="10">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="41"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="21">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="27">
-        <v>180.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="6">
-        <v>175.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="17">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="41"/>
+    </row>
     <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
-    </row>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="I15 I3:I4 I8:I11" name="Range1_1"/>
-    <protectedRange sqref="D40:D41" name="Range1_1_4"/>
+    <protectedRange sqref="D45:D46" name="Range1_1_4"/>
     <protectedRange sqref="D14 D16:D18 D9:D12 D6" name="Range1_1_1"/>
     <protectedRange sqref="D8 D15" name="Range1_1_1_1"/>
     <protectedRange sqref="D13" name="Range1_1_2"/>
